--- a/archive/2026-03/ETF_Investment_Portfolio_20260320.xlsx
+++ b/archive/2026-03/ETF_Investment_Portfolio_20260320.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,901 +454,829 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15336000</v>
+        <v>557000</v>
       </c>
       <c r="D2" t="n">
-        <v>1.28</v>
+        <v>5.9144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1501000</v>
+        <v>303000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.13</v>
+        <v>5.026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8827000</v>
+        <v>538000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.43</v>
+        <v>4.9098</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3885000</v>
+        <v>396000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.24</v>
+        <v>4.4549</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2000</v>
+        <v>105000</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4.3452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4926000</v>
+        <v>1250000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>4.1684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4309000</v>
+        <v>347000</v>
       </c>
       <c r="D8" t="n">
-        <v>6.77</v>
+        <v>4.0132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10703000</v>
+        <v>184000</v>
       </c>
       <c r="D9" t="n">
-        <v>3.09</v>
+        <v>3.8706</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4405000</v>
+        <v>331000</v>
       </c>
       <c r="D10" t="n">
-        <v>8.640000000000001</v>
+        <v>3.8566</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3034000</v>
+        <v>2381000</v>
       </c>
       <c r="D11" t="n">
-        <v>5.21</v>
+        <v>3.5532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5000</v>
+        <v>628000</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3.4278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5765000</v>
+        <v>635000</v>
       </c>
       <c r="D13" t="n">
-        <v>6.07</v>
+        <v>3.3458</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2427000</v>
+        <v>133000</v>
       </c>
       <c r="D14" t="n">
-        <v>7.27</v>
+        <v>3.1756</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>573000</v>
+        <v>328000</v>
       </c>
       <c r="D15" t="n">
-        <v>0.57</v>
+        <v>3.0027</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1305000</v>
+        <v>136000</v>
       </c>
       <c r="D16" t="n">
-        <v>0.33</v>
+        <v>2.7906</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5000</v>
+        <v>840000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2.7047</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7062000</v>
+        <v>267000</v>
       </c>
       <c r="D18" t="n">
-        <v>2.32</v>
+        <v>2.5362</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>486000</v>
+        <v>274000</v>
       </c>
       <c r="D19" t="n">
-        <v>0.88</v>
+        <v>2.2882</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02</v>
+        <v>1.8674</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2876000</v>
+        <v>164000</v>
       </c>
       <c r="D21" t="n">
-        <v>6.28</v>
+        <v>1.8167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7410000</v>
+        <v>2530000</v>
       </c>
       <c r="D22" t="n">
-        <v>4.38</v>
+        <v>1.7062</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5000</v>
+        <v>252000</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1.322</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2657000</v>
+        <v>129000</v>
       </c>
       <c r="D24" t="n">
-        <v>1.08</v>
+        <v>1.2735</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1576000</v>
+        <v>163000</v>
       </c>
       <c r="D25" t="n">
-        <v>0.55</v>
+        <v>1.2489</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>優群</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>355000</v>
+        <v>748000</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06</v>
+        <v>1.1548</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1789000</v>
+        <v>53000</v>
       </c>
       <c r="D27" t="n">
-        <v>0.29</v>
+        <v>1.1453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>158000</v>
+        <v>194000</v>
       </c>
       <c r="D28" t="n">
-        <v>0.18</v>
+        <v>1.1134</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1425000</v>
+        <v>207000</v>
       </c>
       <c r="D29" t="n">
-        <v>0.34</v>
+        <v>1.0954</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>245000</v>
+        <v>345000</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100000</v>
+        <v>1154000</v>
       </c>
       <c r="D31" t="n">
-        <v>0.22</v>
+        <v>1.0663</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1328000</v>
+        <v>504000</v>
       </c>
       <c r="D32" t="n">
-        <v>5.45</v>
+        <v>1.0254</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>530000</v>
+        <v>552000</v>
       </c>
       <c r="D33" t="n">
-        <v>1.91</v>
+        <v>1.0011</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2525848</v>
+        <v>452013</v>
       </c>
       <c r="D34" t="n">
-        <v>4.91</v>
+        <v>0.9949</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4258000</v>
+        <v>44000</v>
       </c>
       <c r="D35" t="n">
-        <v>1.56</v>
+        <v>0.9849</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1036000</v>
+        <v>61000</v>
       </c>
       <c r="D36" t="n">
-        <v>0.45</v>
+        <v>0.9715</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>255000</v>
+        <v>168000</v>
       </c>
       <c r="D37" t="n">
-        <v>3.19</v>
+        <v>0.8601</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3848000</v>
+        <v>534920</v>
       </c>
       <c r="D38" t="n">
-        <v>0.48</v>
+        <v>0.7982</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1704000</v>
+        <v>279000</v>
       </c>
       <c r="D39" t="n">
-        <v>1.08</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3399000</v>
+        <v>122000</v>
       </c>
       <c r="D40" t="n">
-        <v>0.35</v>
+        <v>0.7037</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1366000</v>
+        <v>38000</v>
       </c>
       <c r="D41" t="n">
-        <v>5.62</v>
+        <v>0.7023</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>844000</v>
+        <v>58000</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.6574</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1700000</v>
+        <v>341000</v>
       </c>
       <c r="D43" t="n">
-        <v>0.85</v>
+        <v>0.4012</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>590000</v>
+        <v>110000</v>
       </c>
       <c r="D44" t="n">
-        <v>2.26</v>
+        <v>0.3687</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>248000</v>
+        <v>193000</v>
       </c>
       <c r="D45" t="n">
-        <v>2.1</v>
+        <v>0.3229</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>73000</v>
+        <v>52000</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3</v>
+        <v>0.3193</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>682000</v>
+        <v>413000</v>
       </c>
       <c r="D47" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>4656000</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>勤誠</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1621000</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>金居</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1864000</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>315000</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.31</v>
+        <v>0.2891</v>
       </c>
     </row>
   </sheetData>
@@ -1362,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,952 +1323,876 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15336000</v>
+        <v>557000</v>
       </c>
       <c r="D2" t="n">
-        <v>1.28</v>
+        <v>5.9144</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1501000</v>
+        <v>303000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.13</v>
+        <v>5.026</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8827000</v>
+        <v>538000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.43</v>
+        <v>4.9098</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3885000</v>
+        <v>396000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.24</v>
+        <v>4.4549</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2000</v>
+        <v>105000</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4.3452</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4926000</v>
+        <v>1250000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>4.1684</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4309000</v>
+        <v>347000</v>
       </c>
       <c r="D8" t="n">
-        <v>6.77</v>
+        <v>4.0132</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10703000</v>
+        <v>184000</v>
       </c>
       <c r="D9" t="n">
-        <v>3.09</v>
+        <v>3.8706</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4405000</v>
+        <v>331000</v>
       </c>
       <c r="D10" t="n">
-        <v>8.640000000000001</v>
+        <v>3.8566</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3034000</v>
+        <v>2381000</v>
       </c>
       <c r="D11" t="n">
-        <v>5.21</v>
+        <v>3.5532</v>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5000</v>
+        <v>628000</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3.4278</v>
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5765000</v>
+        <v>635000</v>
       </c>
       <c r="D13" t="n">
-        <v>6.07</v>
+        <v>3.3458</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2427000</v>
+        <v>133000</v>
       </c>
       <c r="D14" t="n">
-        <v>7.27</v>
+        <v>3.1756</v>
       </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>573000</v>
+        <v>328000</v>
       </c>
       <c r="D15" t="n">
-        <v>0.57</v>
+        <v>3.0027</v>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1305000</v>
+        <v>136000</v>
       </c>
       <c r="D16" t="n">
-        <v>0.33</v>
+        <v>2.7906</v>
       </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5000</v>
+        <v>840000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2.7047</v>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7062000</v>
+        <v>267000</v>
       </c>
       <c r="D18" t="n">
-        <v>2.32</v>
+        <v>2.5362</v>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>486000</v>
+        <v>274000</v>
       </c>
       <c r="D19" t="n">
-        <v>0.88</v>
+        <v>2.2882</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02</v>
+        <v>1.8674</v>
       </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2876000</v>
+        <v>164000</v>
       </c>
       <c r="D21" t="n">
-        <v>6.28</v>
+        <v>1.8167</v>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7410000</v>
+        <v>2530000</v>
       </c>
       <c r="D22" t="n">
-        <v>4.38</v>
+        <v>1.7062</v>
       </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5000</v>
+        <v>252000</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1.322</v>
       </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2657000</v>
+        <v>129000</v>
       </c>
       <c r="D24" t="n">
-        <v>1.08</v>
+        <v>1.2735</v>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1576000</v>
+        <v>163000</v>
       </c>
       <c r="D25" t="n">
-        <v>0.55</v>
+        <v>1.2489</v>
       </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>優群</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>355000</v>
+        <v>748000</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06</v>
+        <v>1.1548</v>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1789000</v>
+        <v>53000</v>
       </c>
       <c r="D27" t="n">
-        <v>0.29</v>
+        <v>1.1453</v>
       </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>158000</v>
+        <v>194000</v>
       </c>
       <c r="D28" t="n">
-        <v>0.18</v>
+        <v>1.1134</v>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1425000</v>
+        <v>207000</v>
       </c>
       <c r="D29" t="n">
-        <v>0.34</v>
+        <v>1.0954</v>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>245000</v>
+        <v>345000</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.091</v>
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100000</v>
+        <v>1154000</v>
       </c>
       <c r="D31" t="n">
-        <v>0.22</v>
+        <v>1.0663</v>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1328000</v>
+        <v>504000</v>
       </c>
       <c r="D32" t="n">
-        <v>5.45</v>
+        <v>1.0254</v>
       </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>530000</v>
+        <v>552000</v>
       </c>
       <c r="D33" t="n">
-        <v>1.91</v>
+        <v>1.0011</v>
       </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2525848</v>
+        <v>452013</v>
       </c>
       <c r="D34" t="n">
-        <v>4.91</v>
+        <v>0.9949</v>
       </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4258000</v>
+        <v>44000</v>
       </c>
       <c r="D35" t="n">
-        <v>1.56</v>
+        <v>0.9849</v>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1036000</v>
+        <v>61000</v>
       </c>
       <c r="D36" t="n">
-        <v>0.45</v>
+        <v>0.9715</v>
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>255000</v>
+        <v>168000</v>
       </c>
       <c r="D37" t="n">
-        <v>3.19</v>
+        <v>0.8601</v>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3848000</v>
+        <v>534920</v>
       </c>
       <c r="D38" t="n">
-        <v>0.48</v>
+        <v>0.7982</v>
       </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1704000</v>
+        <v>279000</v>
       </c>
       <c r="D39" t="n">
-        <v>1.08</v>
+        <v>0.731</v>
       </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3399000</v>
+        <v>122000</v>
       </c>
       <c r="D40" t="n">
-        <v>0.35</v>
+        <v>0.7037</v>
       </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1366000</v>
+        <v>38000</v>
       </c>
       <c r="D41" t="n">
-        <v>5.62</v>
+        <v>0.7023</v>
       </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>844000</v>
+        <v>58000</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.6574</v>
       </c>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1700000</v>
+        <v>341000</v>
       </c>
       <c r="D43" t="n">
-        <v>0.85</v>
+        <v>0.4012</v>
       </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>590000</v>
+        <v>110000</v>
       </c>
       <c r="D44" t="n">
-        <v>2.26</v>
+        <v>0.3687</v>
       </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>248000</v>
+        <v>193000</v>
       </c>
       <c r="D45" t="n">
-        <v>2.1</v>
+        <v>0.3229</v>
       </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>73000</v>
+        <v>52000</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3</v>
+        <v>0.3193</v>
       </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>682000</v>
+        <v>413000</v>
       </c>
       <c r="D47" t="n">
-        <v>1.45</v>
+        <v>0.2891</v>
       </c>
       <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>4656000</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>勤誠</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1621000</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>金居</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1864000</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>315000</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
